--- a/스터디 벌금 관리.xlsx
+++ b/스터디 벌금 관리.xlsx
@@ -501,6 +501,12 @@
       <c r="C11">
         <v>5000</v>
       </c>
+      <c r="G11">
+        <v>5000</v>
+      </c>
+      <c r="H11">
+        <v>5000</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
